--- a/TJ_Surgery_2018_2023_Pitchers_Trimmed.xlsx
+++ b/TJ_Surgery_2018_2023_Pitchers_Trimmed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6772c73964c7b6d/TJPROJECT599/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_A6A15F67D34BAA6FE9739CD75E5DCE3A17CAB807" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C45B8933-521C-4B93-89D0-014E5BBC9613}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_A6A15F67D34BAA6FE9739CD75E5DCE3A17CAB807" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07AD73CD-A382-45A8-9ED6-BA5F33E07893}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="225">
   <si>
     <t>Player</t>
   </si>
@@ -692,6 +692,9 @@
   </si>
   <si>
     <t>Nik Turley</t>
+  </si>
+  <si>
+    <t>FgID</t>
   </si>
 </sst>
 </file>
@@ -769,6 +772,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1056,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U159"/>
+  <dimension ref="A1:V159"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1079,7 +1086,7 @@
     <col min="21" max="21" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1143,8 +1150,11 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V1" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1185,7 +1195,7 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
@@ -1226,7 +1236,7 @@
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1267,7 +1277,7 @@
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1308,7 +1318,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -1349,7 +1359,7 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -1390,7 +1400,7 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -1431,7 +1441,7 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -1472,7 +1482,7 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1513,7 +1523,7 @@
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>46</v>
       </c>
@@ -1552,7 +1562,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
@@ -1593,7 +1603,7 @@
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
@@ -1634,7 +1644,7 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -1675,7 +1685,7 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>55</v>
       </c>
@@ -1716,7 +1726,7 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>58</v>
       </c>
